--- a/docs/notebooks/hash_table.xlsx
+++ b/docs/notebooks/hash_table.xlsx
@@ -1824,7 +1824,7 @@
     </row>
     <row r="290" spans="1:1">
       <c r="A290">
-        <v>1.127766143616049</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="291" spans="1:1">
@@ -3444,7 +3444,7 @@
     </row>
     <row r="614" spans="1:1">
       <c r="A614">
-        <v>1.127766143616071</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="615" spans="1:1">
@@ -11934,7 +11934,7 @@
     </row>
     <row r="2312" spans="1:1">
       <c r="A2312">
-        <v>2.416593574757875</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="2313" spans="1:1">
@@ -13344,7 +13344,7 @@
     </row>
     <row r="2594" spans="1:1">
       <c r="A2594">
-        <v>1.127766143616071</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="2595" spans="1:1">
@@ -30399,7 +30399,7 @@
     </row>
     <row r="6005" spans="1:1">
       <c r="A6005">
-        <v>1.127766143616016</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="6006" spans="1:1">
@@ -32604,7 +32604,7 @@
     </row>
     <row r="6446" spans="1:1">
       <c r="A6446">
-        <v>1.127766143616082</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="6447" spans="1:1">
@@ -33279,7 +33279,7 @@
     </row>
     <row r="6581" spans="1:1">
       <c r="A6581">
-        <v>1.12776614361606</v>
+        <v>1.127766143616094</v>
       </c>
     </row>
     <row r="6582" spans="1:1">
@@ -33369,7 +33369,7 @@
     </row>
     <row r="6599" spans="1:1">
       <c r="A6599">
-        <v>1.127766143616016</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="6600" spans="1:1">
@@ -33459,7 +33459,7 @@
     </row>
     <row r="6617" spans="1:1">
       <c r="A6617">
-        <v>1.12776614361606</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="6618" spans="1:1">
